--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -7785,7 +7785,7 @@
         <v>120710210</v>
       </c>
       <c r="B60" t="n">
-        <v>91991</v>
+        <v>92001</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -7785,7 +7785,7 @@
         <v>120710210</v>
       </c>
       <c r="B60" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -7785,7 +7785,7 @@
         <v>120710210</v>
       </c>
       <c r="B60" t="n">
-        <v>92013</v>
+        <v>92014</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7899,6 +7899,126 @@
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>124018379</v>
+      </c>
+      <c r="B61" t="n">
+        <v>95529</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>210</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Björklund, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>595537</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6550897</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På klen granlåga ca 7 cm strax söder om roten på en grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8019,6 +8019,120 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132738300</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91330</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4189</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kamjordstjärna</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Geastrum pectinatum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Björklund, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>595547</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6550918</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ett fjolårsexemplar i barrmatta under gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -8024,7 +8024,7 @@
         <v>132738300</v>
       </c>
       <c r="B62" t="n">
-        <v>91330</v>
+        <v>91331</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17283021</v>
+        <v>54795735</v>
       </c>
       <c r="B2" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -725,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595544.1741117467</v>
+        <v>595555</v>
       </c>
       <c r="R2" t="n">
-        <v>6550884.239137802</v>
+        <v>6550778</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,27 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Äldre granskog i svag ostvänd sluttning.</t>
+          <t>Gammal grandominerad skog. 4 fruktkroppar i anslutning till vildsvinsbökad mark. Vid fastighetsgräns.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17283027</v>
+        <v>54798406</v>
       </c>
       <c r="B3" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,26 +799,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595584.0489560144</v>
+        <v>595463</v>
       </c>
       <c r="R3" t="n">
-        <v>6550854.902504279</v>
+        <v>6551071</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,27 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre granskog.</t>
+          <t>Äldre grandominerad skog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,15 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17283016</v>
+        <v>54799193</v>
       </c>
       <c r="B4" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,26 +912,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595562.011802766</v>
+        <v>595539</v>
       </c>
       <c r="R4" t="n">
-        <v>6550933.010738119</v>
+        <v>6550967</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1011,27 +976,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Äldre granskog i östvänd svag sluttning.</t>
+          <t>Svag nordsluttning med äldre granskog. Intressant svampflora med flera rödlistade arter.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17282910</v>
+        <v>55505222</v>
       </c>
       <c r="B5" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,26 +1025,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1109,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595534.7659661601</v>
+        <v>595599</v>
       </c>
       <c r="R5" t="n">
-        <v>6551034.121521861</v>
+        <v>6550831</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1139,27 +1089,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre granskog i no-vänd sluttning. Tidigare gallrad.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,60 +1127,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17283025</v>
+        <v>54797582</v>
       </c>
       <c r="B6" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595582.9425226033</v>
+        <v>595557</v>
       </c>
       <c r="R6" t="n">
-        <v>6550857.959549031</v>
+        <v>6550781</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1267,27 +1203,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>25 fruktkroppar på ca 20x10m stort område i äldre granskog.</t>
+          <t>Gammal rötskadad granstubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,7 +1222,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1315,60 +1240,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17283017</v>
+        <v>54798261</v>
       </c>
       <c r="B7" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595579.9106891969</v>
+        <v>595567</v>
       </c>
       <c r="R7" t="n">
-        <v>6550938.084801617</v>
+        <v>6550842</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1395,27 +1316,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mellan två granlågor i äldre granskog ca 10-15m från öppen mark.</t>
+          <t>Gammal granlåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1335,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1443,60 +1353,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17283023</v>
+        <v>54798335</v>
       </c>
       <c r="B8" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595564.0793723884</v>
+        <v>595508</v>
       </c>
       <c r="R8" t="n">
-        <v>6550870.855279646</v>
+        <v>6551030</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1523,27 +1429,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre granskog. Tidigare gallrat.</t>
+          <t>Gammal rötskadad granstubbe.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1552,7 +1448,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1571,60 +1466,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17283030</v>
+        <v>54798350</v>
       </c>
       <c r="B9" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595591.8068747378</v>
+        <v>595463</v>
       </c>
       <c r="R9" t="n">
-        <v>6550832.989333222</v>
+        <v>6551032</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1651,27 +1542,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre granskog. Sammantaget en riklig förekomst av bombmurklor längs en stor del av granbeståndet.</t>
+          <t>Gammal granlåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,7 +1561,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1699,60 +1579,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17282897</v>
+        <v>55505077</v>
       </c>
       <c r="B10" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595531.8688035626</v>
+        <v>595560</v>
       </c>
       <c r="R10" t="n">
-        <v>6551005.774099369</v>
+        <v>6550783</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1779,27 +1655,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>70 fruktkroppar på ca 40x30m stort område i no-vänd sluttning. Ca 70-80årig granskog. Tidigare gallrad.</t>
+          <t>På rötskadad granstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1808,7 +1674,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1827,60 +1692,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17283015</v>
+        <v>55505458</v>
       </c>
       <c r="B11" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595549.803053525</v>
+        <v>595471</v>
       </c>
       <c r="R11" t="n">
-        <v>6550968.178819312</v>
+        <v>6551015</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1907,27 +1768,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>10 fruktkroppar på ca 15x10m stort område i äldre granskog. Tidigare gallrat. Svag no-sluttning.</t>
+          <t>Rötskada granlåga.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1936,7 +1787,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1955,60 +1805,56 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17282893</v>
+        <v>55506717</v>
       </c>
       <c r="B12" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595520.1095230723</v>
+        <v>595555</v>
       </c>
       <c r="R12" t="n">
-        <v>6551022.959633837</v>
+        <v>6550868</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2035,27 +1881,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>31 bombmurklor på ca 20x10m stort område i nordost-vänd sluttning. Grandominerad skog ca 60-80år. Tidigare gallrat.</t>
+          <t>På rötskadad granlåga.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,7 +1900,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2076,67 +1911,64 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17283020</v>
+        <v>112557966</v>
       </c>
       <c r="B13" t="n">
-        <v>81972</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595553.1707142543</v>
+        <v>595502</v>
       </c>
       <c r="R13" t="n">
-        <v>6550915.824439319</v>
+        <v>6550929</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2163,27 +1995,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre granskog. Nära liten bergklack.</t>
+          <t>Nära roten på gammal granlåga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2211,15 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>54799155</v>
+        <v>112557989</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,36 +2044,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595547.9410223542</v>
+        <v>595556</v>
       </c>
       <c r="R14" t="n">
-        <v>6551022.112364363</v>
+        <v>6550792</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2283,22 +2110,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Vid roten på gammal granlåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,15 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54798393</v>
+        <v>116084668</v>
       </c>
       <c r="B15" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,36 +2159,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>210</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595472.0166348737</v>
+        <v>595490</v>
       </c>
       <c r="R15" t="n">
-        <v>6551072.139780834</v>
+        <v>6550951</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2398,22 +2225,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På nedre delen av gammal granlåga.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2441,60 +2263,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>54798406</v>
+        <v>124018379</v>
       </c>
       <c r="B16" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595462.7780603276</v>
+        <v>595537</v>
       </c>
       <c r="R16" t="n">
-        <v>6551070.881062903</v>
+        <v>6550897</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2521,27 +2340,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog.</t>
+          <t>På klen granlåga ca 7 cm strax söder om roten på en grov granlåga.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2569,42 +2378,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54796885</v>
+        <v>55506898</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2619,10 +2423,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595557.9101445</v>
+        <v>595549</v>
       </c>
       <c r="R17" t="n">
-        <v>6550787.928195721</v>
+        <v>6550978</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2649,27 +2453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog. 15 fruktkroppar i anslutning till vildsvinsbökad mark. Vid fastighetsgräns.</t>
+          <t>I gammal barrblandskog. Svampinventering med några deltagare i Stockholms svampvänner.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2690,22 +2484,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>54795236</v>
+        <v>54798297</v>
       </c>
       <c r="B18" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2713,26 +2502,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2747,10 +2536,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595567.8694440859</v>
+        <v>595546</v>
       </c>
       <c r="R18" t="n">
-        <v>6550780.979216861</v>
+        <v>6550909</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2780,24 +2569,14 @@
           <t>2015-08-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2015-08-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>En liten fruktkropp på granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2825,41 +2604,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54798412</v>
+        <v>17282893</v>
       </c>
       <c r="B19" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2867,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595502.8236846365</v>
+        <v>595520</v>
       </c>
       <c r="R19" t="n">
-        <v>6551117.11978308</v>
+        <v>6551023</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2897,22 +2679,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>31 bombmurklor på ca 20x10m stort område i nordost-vänd sluttning. Grandominerad skog ca 60-80år. Tidigare gallrat.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2940,41 +2717,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>54799303</v>
+        <v>17282897</v>
       </c>
       <c r="B20" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2982,10 +2762,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595583.8729866347</v>
+        <v>595532</v>
       </c>
       <c r="R20" t="n">
-        <v>6550923.788866451</v>
+        <v>6551006</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3012,22 +2792,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>70 fruktkroppar på ca 40x30m stort område i no-vänd sluttning. Ca 70-80årig granskog. Tidigare gallrad.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,42 +2830,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>54798233</v>
+        <v>17282910</v>
       </c>
       <c r="B21" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4366</v>
+        <v>1445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3105,10 +2875,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595584.8845756508</v>
+        <v>595535</v>
       </c>
       <c r="R21" t="n">
-        <v>6550842.070490922</v>
+        <v>6551034</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3135,27 +2905,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog rikligt påverkad av vildsvinsbök.</t>
+          <t>Äldre granskog i no-vänd sluttning. Tidigare gallrad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3183,61 +2943,55 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>54798261</v>
+        <v>17283015</v>
       </c>
       <c r="B22" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>210</v>
+        <v>1445</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>595566.8569011926</v>
+        <v>595550</v>
       </c>
       <c r="R22" t="n">
-        <v>6550842.13425314</v>
+        <v>6550968</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3264,27 +3018,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gammal granlåga.</t>
+          <t>10 fruktkroppar på ca 15x10m stort område i äldre granskog. Tidigare gallrat. Svag no-sluttning.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,6 +3037,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3311,41 +3056,44 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54798385</v>
+        <v>17283016</v>
       </c>
       <c r="B23" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3353,10 +3101,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>595449.8578807391</v>
+        <v>595562</v>
       </c>
       <c r="R23" t="n">
-        <v>6551052.051578638</v>
+        <v>6550933</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3383,22 +3131,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre granskog i östvänd svag sluttning.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3426,61 +3169,55 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>54798350</v>
+        <v>17283017</v>
       </c>
       <c r="B24" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>210</v>
+        <v>1445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>595463.2377267247</v>
+        <v>595580</v>
       </c>
       <c r="R24" t="n">
-        <v>6551031.8218813</v>
+        <v>6550938</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3507,27 +3244,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gammal granlåga.</t>
+          <t>Mellan två granlågor i äldre granskog ca 10-15m från öppen mark.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3536,6 +3263,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3554,61 +3282,55 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>54798335</v>
+        <v>17283020</v>
       </c>
       <c r="B25" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>210</v>
+        <v>1445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595508.0921914611</v>
+        <v>595553</v>
       </c>
       <c r="R25" t="n">
-        <v>6551029.85687769</v>
+        <v>6550916</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3635,27 +3357,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gammal rötskadad granstubbe.</t>
+          <t>Äldre granskog. Nära liten bergklack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3664,6 +3376,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3682,41 +3395,44 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>54799217</v>
+        <v>17283021</v>
       </c>
       <c r="B26" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>1445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3724,10 +3440,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595579.241962177</v>
+        <v>595544</v>
       </c>
       <c r="R26" t="n">
-        <v>6550944.237332858</v>
+        <v>6550884</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3754,22 +3470,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre granskog i svag ostvänd sluttning.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3797,53 +3508,55 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>54798269</v>
+        <v>17283023</v>
       </c>
       <c r="B27" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2170</v>
+        <v>1445</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>595534.8294312474</v>
+        <v>595564</v>
       </c>
       <c r="R27" t="n">
-        <v>6550845.961418635</v>
+        <v>6550871</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3870,27 +3583,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal tallstubbe.</t>
+          <t>Äldre granskog. Tidigare gallrat.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3899,6 +3602,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3917,41 +3621,44 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>54799449</v>
+        <v>17283025</v>
       </c>
       <c r="B28" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>1445</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3959,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>595601.2140601313</v>
+        <v>595583</v>
       </c>
       <c r="R28" t="n">
-        <v>6550848.133773278</v>
+        <v>6550858</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3989,22 +3696,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>25 fruktkroppar på ca 20x10m stort område i äldre granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4032,42 +3734,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>54799193</v>
+        <v>17283027</v>
       </c>
       <c r="B29" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>150</v>
+        <v>1445</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4082,10 +3779,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>595539.0201675883</v>
+        <v>595584</v>
       </c>
       <c r="R29" t="n">
-        <v>6550966.88132705</v>
+        <v>6550855</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4112,27 +3809,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Svag nordsluttning med äldre granskog. Intressant svampflora med flera rödlistade arter.</t>
+          <t>Äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4160,37 +3847,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>54798215</v>
+        <v>17283030</v>
       </c>
       <c r="B30" t="n">
-        <v>90366</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5836</v>
+        <v>1445</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4210,10 +3892,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>595605.858140884</v>
+        <v>595592</v>
       </c>
       <c r="R30" t="n">
-        <v>6550827.171016345</v>
+        <v>6550833</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4240,27 +3922,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre grandominerad skog med rikligt påverkad mark i form av vildsvinsbök.</t>
+          <t>Äldre granskog. Sammantaget en riklig förekomst av bombmurklor längs en stor del av granbeståndet.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4288,42 +3960,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>54798239</v>
+        <v>116084132</v>
       </c>
       <c r="B31" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>1445</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4332,16 +3999,17 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595598.1514831838</v>
+        <v>595587</v>
       </c>
       <c r="R31" t="n">
-        <v>6550847.029015319</v>
+        <v>6550861</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4368,22 +4036,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>I anslutning till barr- och mossmatta vid äldre gran. Återfynd från tidigare känd lokal. Strax söder om fyndplatsen har granbarkborrar angripit granarna.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4411,37 +4074,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>54798297</v>
+        <v>116084465</v>
       </c>
       <c r="B32" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1339</v>
+        <v>1445</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4455,16 +4113,17 @@
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595546.1317252616</v>
+        <v>595570</v>
       </c>
       <c r="R32" t="n">
-        <v>6550908.965252068</v>
+        <v>6550879</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4491,27 +4150,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2015-08-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>En liten fruktkropp på granlåga.</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4539,52 +4183,56 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>55506884</v>
+        <v>116084603</v>
       </c>
       <c r="B33" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4363</v>
+        <v>1445</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>595554.911482604</v>
+        <v>595573</v>
       </c>
       <c r="R33" t="n">
-        <v>6550969.848706424</v>
+        <v>6550888</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4611,27 +4259,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Svampinventering med några deltagare i Stockholms svampvänner.</t>
+          <t>Vid äldre gran med en klenare lutad gran mot denna.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4652,49 +4290,44 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>55505222</v>
+        <v>116084966</v>
       </c>
       <c r="B34" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>150</v>
+        <v>1445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4703,16 +4336,17 @@
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>595599.0641812151</v>
+        <v>595516</v>
       </c>
       <c r="R34" t="n">
-        <v>6550831.114194849</v>
+        <v>6551021</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4739,27 +4373,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre barrblandskog.</t>
+          <t>Återfynd på tidigare känd lokal. !00 observerade fruktkroppar i anslutning till övre delen av östvänd sluttning med äldre granskog på mossrik mark. De är spridda på ett område av ca 20x50m. Strax norr om fyndplatsen har granbarkborrarna angripit granskogen.På grund av att många av de kända bombmurkellokalerna är spolierade av granbarkborrar är det viktigt att skydda de kvarvarande lokalerna. Verkar vara ett bra år för bombmurklor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4787,41 +4411,44 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55505501</v>
+        <v>55506746</v>
       </c>
       <c r="B35" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5964</v>
+        <v>2008</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4829,10 +4456,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>595485.9257805605</v>
+        <v>595571</v>
       </c>
       <c r="R35" t="n">
-        <v>6551071.972840181</v>
+        <v>6550935</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4859,22 +4486,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>15 ex i barrmattan under gammal gran. Svampinventering med några deltagare i Stockholms svampvänner.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4895,49 +4517,44 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55505418</v>
+        <v>55506806</v>
       </c>
       <c r="B36" t="n">
-        <v>88853</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4189</v>
+        <v>2008</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4952,10 +4569,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>595507.8212074975</v>
+        <v>595564</v>
       </c>
       <c r="R36" t="n">
-        <v>6551020.0823758</v>
+        <v>6550947</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4982,27 +4599,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>I barrmatta under gammal gran.</t>
+          <t>I barrmattan under gammal gran. Svampinventering med några deltagare i Stockholms svampvänner.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5023,59 +4630,63 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>55505914</v>
+        <v>112557762</v>
       </c>
       <c r="B37" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>2008</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>595550.2564045949</v>
+        <v>595561</v>
       </c>
       <c r="R37" t="n">
-        <v>6551011.888336989</v>
+        <v>6550947</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5102,22 +4713,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Grandominerad skog fortfarande oangripen av granbarkborrar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5145,15 +4751,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>55506746</v>
+        <v>120710162</v>
       </c>
       <c r="B38" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5175,12 +4776,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5189,16 +4790,17 @@
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>595571.2378522804</v>
+        <v>595528</v>
       </c>
       <c r="R38" t="n">
-        <v>6550934.783513897</v>
+        <v>6550919</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5225,27 +4827,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>15 ex i barrmattan under gammal gran. Svampinventering med några deltagare i Stockholms svampvänner.</t>
+          <t>Granskogen fortfarande vital. Tyvärr har granbarkborrar angripit och dödat en stor del av granskogen i nära anslutning.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5266,67 +4858,55 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>55506898</v>
+        <v>54798269</v>
       </c>
       <c r="B39" t="n">
-        <v>85177</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>445</v>
+        <v>2170</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>595549.0445558249</v>
+        <v>595535</v>
       </c>
       <c r="R39" t="n">
-        <v>6550977.92775027</v>
+        <v>6550846</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5353,27 +4933,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>I gammal barrblandskog. Svampinventering med några deltagare i Stockholms svampvänner.</t>
+          <t>På gammal tallstubbe.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5382,7 +4952,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5394,22 +4963,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>55506717</v>
+        <v>116084633</v>
       </c>
       <c r="B40" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5417,45 +4981,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>2810</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>595554.8788300528</v>
+        <v>595543</v>
       </c>
       <c r="R40" t="n">
-        <v>6550868.054912587</v>
+        <v>6550901</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5482,27 +5047,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På rötskadad granlåga.</t>
+          <t>På mindre sten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5511,6 +5066,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5522,22 +5078,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55505828</v>
+        <v>55505418</v>
       </c>
       <c r="B41" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5545,25 +5096,33 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4366</v>
+        <v>4189</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5571,10 +5130,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>595545.8052918481</v>
+        <v>595508</v>
       </c>
       <c r="R41" t="n">
-        <v>6551025.143575211</v>
+        <v>6551020</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5604,19 +5163,14 @@
           <t>2015-09-24</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2015-09-24</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>I barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5644,15 +5198,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>55505315</v>
+        <v>112557797</v>
       </c>
       <c r="B42" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91330</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5660,36 +5209,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>4189</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>595537.8368179434</v>
+        <v>595543</v>
       </c>
       <c r="R42" t="n">
-        <v>6550973.020963751</v>
+        <v>6551028</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5716,22 +5274,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-13</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5759,15 +5307,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>55505077</v>
+        <v>132738300</v>
       </c>
       <c r="B43" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91395</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5775,21 +5318,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>210</v>
+        <v>4189</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5799,24 +5342,24 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>595560.097343059</v>
+        <v>595547</v>
       </c>
       <c r="R43" t="n">
-        <v>6550782.841585587</v>
+        <v>6550918</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5840,27 +5383,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På rötskadad granstubbe.</t>
+          <t>Ett fjolårsexemplar i barrmatta under gammal gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5869,6 +5402,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5887,15 +5421,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>55505458</v>
+        <v>55506884</v>
       </c>
       <c r="B44" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5903,45 +5432,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>210</v>
+        <v>4363</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>595470.8664078788</v>
+        <v>595555</v>
       </c>
       <c r="R44" t="n">
-        <v>6551015.047238187</v>
+        <v>6550970</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5968,27 +5488,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-09-26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rötskada granlåga.</t>
+          <t>Svampinventering med några deltagare i Stockholms svampvänner.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5997,6 +5507,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6008,22 +5519,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>55506806</v>
+        <v>54798233</v>
       </c>
       <c r="B45" t="n">
-        <v>88856</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6031,26 +5537,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2008</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6065,10 +5571,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>595564.2387760285</v>
+        <v>595585</v>
       </c>
       <c r="R45" t="n">
-        <v>6550946.947151789</v>
+        <v>6550842</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6095,27 +5601,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>I barrmattan under gammal gran. Svampinventering med några deltagare i Stockholms svampvänner.</t>
+          <t>Äldre grandominerad skog rikligt påverkad av vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6136,48 +5632,51 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>55505278</v>
+        <v>54798239</v>
       </c>
       <c r="B46" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6185,10 +5684,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>595613.7585813332</v>
+        <v>595598</v>
       </c>
       <c r="R46" t="n">
-        <v>6550820.170780434</v>
+        <v>6550847</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6215,22 +5714,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6258,37 +5747,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>55505499</v>
+        <v>54798393</v>
       </c>
       <c r="B47" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6300,10 +5784,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>595466.7526166149</v>
+        <v>595472</v>
       </c>
       <c r="R47" t="n">
-        <v>6551056.071753114</v>
+        <v>6551072</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6330,22 +5814,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2015-09-24</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6373,61 +5847,47 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112557797</v>
+        <v>54799155</v>
       </c>
       <c r="B48" t="n">
-        <v>89122</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4189</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>595543</v>
+        <v>595548</v>
       </c>
       <c r="R48" t="n">
-        <v>6551029</v>
+        <v>6551022</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6454,12 +5914,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6487,62 +5947,47 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112557989</v>
+        <v>54799217</v>
       </c>
       <c r="B49" t="n">
-        <v>93540</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>210</v>
+        <v>4366</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>595556</v>
+        <v>595579</v>
       </c>
       <c r="R49" t="n">
-        <v>6550792</v>
+        <v>6550944</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6569,17 +6014,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Vid roten på gammal granlåga.</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6607,15 +6047,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112557762</v>
+        <v>55505315</v>
       </c>
       <c r="B50" t="n">
-        <v>89125</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6623,45 +6058,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2008</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>595561</v>
+        <v>595538</v>
       </c>
       <c r="R50" t="n">
-        <v>6550947</v>
+        <v>6550973</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6688,17 +6114,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Grandominerad skog fortfarande oangripen av granbarkborrar.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6726,62 +6147,47 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112557966</v>
+        <v>55505828</v>
       </c>
       <c r="B51" t="n">
-        <v>93540</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>210</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>595502</v>
+        <v>595546</v>
       </c>
       <c r="R51" t="n">
-        <v>6550929</v>
+        <v>6551025</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6808,17 +6214,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Nära roten på gammal granlåga.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6846,61 +6247,47 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>116084132</v>
+        <v>55505914</v>
       </c>
       <c r="B52" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1445</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>595587</v>
+        <v>595550</v>
       </c>
       <c r="R52" t="n">
-        <v>6550861</v>
+        <v>6551012</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6927,17 +6314,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I anslutning till barr- och mossmatta vid äldre gran. Återfynd från tidigare känd lokal. Strax söder om fyndplatsen har granbarkborrar angripit granarna.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6965,49 +6347,36 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116084465</v>
+        <v>116084689</v>
       </c>
       <c r="B53" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1445</v>
+        <v>4660</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -7016,10 +6385,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>595570</v>
+        <v>595534</v>
       </c>
       <c r="R53" t="n">
-        <v>6550879</v>
+        <v>6551051</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -7052,6 +6421,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-04-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På asplåga.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7079,15 +6453,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>116084668</v>
+        <v>54798215</v>
       </c>
       <c r="B54" t="n">
-        <v>94284</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7095,46 +6464,44 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>210</v>
+        <v>5836</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>595490</v>
+        <v>595606</v>
       </c>
       <c r="R54" t="n">
-        <v>6550951</v>
+        <v>6550827</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7161,17 +6528,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På nedre delen av gammal granlåga.</t>
+          <t>Äldre grandominerad skog med rikligt påverkad mark i form av vildsvinsbök.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7199,42 +6566,37 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>116084966</v>
+        <v>54795236</v>
       </c>
       <c r="B55" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1445</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7243,17 +6605,16 @@
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>595516</v>
+        <v>595568</v>
       </c>
       <c r="R55" t="n">
-        <v>6551021</v>
+        <v>6550781</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7280,17 +6641,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Återfynd på tidigare känd lokal. !00 observerade fruktkroppar i anslutning till övre delen av östvänd sluttning med äldre granskog på mossrik mark. De är spridda på ett område av ca 20x50m. Strax norr om fyndplatsen har granbarkborrarna angripit granskogen.På grund av att många av de kända bombmurkellokalerna är spolierade av granbarkborrar är det viktigt att skydda de kvarvarande lokalerna. Verkar vara ett bra år för bombmurklor.</t>
+          <t>Äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7318,61 +6679,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>116084603</v>
+        <v>54798385</v>
       </c>
       <c r="B56" t="n">
-        <v>83054</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1445</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>595573</v>
+        <v>595450</v>
       </c>
       <c r="R56" t="n">
-        <v>6550888</v>
+        <v>6551052</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7399,17 +6746,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Vid äldre gran med en klenare lutad gran mot denna.</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7437,62 +6779,47 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>116084633</v>
+        <v>54798412</v>
       </c>
       <c r="B57" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2810</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>595543</v>
+        <v>595503</v>
       </c>
       <c r="R57" t="n">
-        <v>6550901</v>
+        <v>6551117</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7519,17 +6846,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På mindre sten.</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7557,15 +6879,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120710162</v>
+        <v>54799303</v>
       </c>
       <c r="B58" t="n">
-        <v>90117</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7573,45 +6890,36 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2008</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>595528</v>
+        <v>595584</v>
       </c>
       <c r="R58" t="n">
-        <v>6550919</v>
+        <v>6550924</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7638,17 +6946,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Granskogen fortfarande vital. Tyvärr har granbarkborrar angripit och dödat en stor del av granskogen i nära anslutning.</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7676,19 +6979,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120710453</v>
+        <v>54799449</v>
       </c>
       <c r="B59" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7712,17 +7010,16 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>595545</v>
+        <v>595601</v>
       </c>
       <c r="R59" t="n">
-        <v>6550967</v>
+        <v>6550848</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7749,12 +7046,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-08-09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7782,15 +7079,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120710210</v>
+        <v>55505278</v>
       </c>
       <c r="B60" t="n">
-        <v>92014</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7798,45 +7090,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>595556</v>
+        <v>595614</v>
       </c>
       <c r="R60" t="n">
-        <v>6550973</v>
+        <v>6550820</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7863,17 +7146,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Granskogen fortfarande vital. Tyvärr har granbarkborrar angripit och dödat en stor del av granskogen i nära anslutning.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7901,62 +7179,47 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124018379</v>
+        <v>55505499</v>
       </c>
       <c r="B61" t="n">
-        <v>95551</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>210</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>595537</v>
+        <v>595467</v>
       </c>
       <c r="R61" t="n">
-        <v>6550897</v>
+        <v>6551056</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7983,17 +7246,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På klen granlåga ca 7 cm strax söder om roten på en grov granlåga.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8021,59 +7279,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132738300</v>
+        <v>55505501</v>
       </c>
       <c r="B62" t="n">
-        <v>91339</v>
+        <v>93233</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4189</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Björklund, NV om, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>595547</v>
+        <v>595486</v>
       </c>
       <c r="R62" t="n">
-        <v>6550918</v>
+        <v>6551072</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8097,17 +7346,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ett fjolårsexemplar i barrmatta under gammal gran.</t>
+          <t>2015-09-24</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8132,6 +7376,429 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120710453</v>
+      </c>
+      <c r="B63" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Björklund, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>595545</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6550967</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>108379657</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Björklund, NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>595593</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6550977</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Lekande åkergrodor i vattensamling och mindre våtmark.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>54797790</v>
+      </c>
+      <c r="B65" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Björklund, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>595557</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6550781</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2015-08-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2015-08-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Sparsamt spridd inom området.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>54798496</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Björklund, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>595497</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6551143</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mellösa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2015-08-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2015-08-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Enstaka förekomst av blåsippor i området. Kulturhistoriska spår i form av rester av gammal kolbotten och en stensatt eldstad från tidigare kolningsverksamhet.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54631-2022 artfynd.xlsx
+++ b/artfynd/A 54631-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54795735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798406</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54799193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54797582</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798261</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798335</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798350</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505077</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1802,6 +1852,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505458</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1915,6 +1970,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55506717</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2030,6 +2090,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557966</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557989</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2260,6 +2330,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084668</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2375,6 +2450,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124018379</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55506898</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2601,6 +2686,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,6 +2804,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17282893</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2827,6 +2922,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17282897</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2940,6 +3040,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17282910</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3053,6 +3158,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283015</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3166,6 +3276,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283016</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3279,6 +3394,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283017</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3392,6 +3512,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283020</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3505,6 +3630,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283021</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3618,6 +3748,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283023</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3731,6 +3866,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3844,6 +3984,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283027</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3957,6 +4102,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17283030</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4071,6 +4221,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084132</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4180,6 +4335,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084465</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4294,6 +4454,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084603</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4408,6 +4573,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084966</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4521,6 +4691,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55506746</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4634,6 +4809,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55506806</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4748,6 +4928,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557762</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4862,6 +5047,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120710162</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4967,6 +5157,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798269</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5082,6 +5277,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084633</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5195,6 +5395,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505418</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5304,6 +5509,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112557797</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5418,6 +5628,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132738300</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5523,6 +5738,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55506884</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5636,6 +5856,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798233</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5744,6 +5969,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798239</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5844,6 +6074,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798393</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5944,6 +6179,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54799155</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6044,6 +6284,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54799217</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6144,6 +6389,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505315</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6244,6 +6494,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505828</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6344,6 +6599,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505914</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6450,6 +6710,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116084689</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6563,6 +6828,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798215</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6676,6 +6946,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54795236</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6776,6 +7051,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798385</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6876,6 +7156,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798412</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6976,6 +7261,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54799303</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7076,6 +7366,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54799449</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7176,6 +7471,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505278</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7276,6 +7576,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505499</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7376,6 +7681,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55505501</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7477,6 +7787,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120710453</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7589,6 +7904,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108379657</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7694,6 +8014,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54797790</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7799,8 +8124,80 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54798496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>